--- a/documentacion/Catalogo de Datos.xlsx
+++ b/documentacion/Catalogo de Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7460820-15C3-4213-98AB-81E6A5B4CFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322C43CD-C6DB-4AB5-95CD-31B733AD7A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{1F831B13-9E82-406B-B02D-1EAF59D96BE3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F831B13-9E82-406B-B02D-1EAF59D96BE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
   <si>
     <t>numero</t>
   </si>
@@ -754,251 +754,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D33CE82-57EC-47E4-9B49-5C264FA2EEA8}">
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="3">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="3">
-        <v>1</v>
-      </c>
-      <c r="L1" s="3">
-        <v>5</v>
-      </c>
-      <c r="M1" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="3">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="3">
-        <v>5</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="3">
-        <v>3</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="3">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="3">
-        <v>3</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="3">
-        <v>5</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-      <c r="M5" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="3">
-        <v>4</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="3">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>2</v>
-      </c>
-      <c r="M7" s="3">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="3">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1</v>
-      </c>
-      <c r="M8" s="3">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="3">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K9" s="3">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I10" s="3">
-        <v>10</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3">
-        <v>11</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="3">
-        <v>3</v>
-      </c>
-      <c r="L11" s="3">
-        <v>6</v>
-      </c>
-      <c r="M11" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -1020,23 +853,8 @@
       <c r="G12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="3">
-        <v>12</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="3">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -1058,23 +876,8 @@
       <c r="G13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="3">
-        <v>13</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1</v>
-      </c>
-      <c r="L13" s="3">
-        <v>6</v>
-      </c>
-      <c r="M13" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -1096,23 +899,8 @@
       <c r="G14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="3">
-        <v>14</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K14" s="3">
-        <v>6</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1</v>
-      </c>
-      <c r="M14" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>3</v>
       </c>
@@ -1134,23 +922,8 @@
       <c r="G15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="3">
-        <v>15</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
-        <v>6</v>
-      </c>
-      <c r="M15" s="3">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>4</v>
       </c>
@@ -1172,23 +945,8 @@
       <c r="G16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="3">
-        <v>16</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="3">
-        <v>6</v>
-      </c>
-      <c r="L16" s="3">
-        <v>5</v>
-      </c>
-      <c r="M16" s="3">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>5</v>
       </c>
@@ -1210,23 +968,8 @@
       <c r="G17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="3">
-        <v>17</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3">
-        <v>7</v>
-      </c>
-      <c r="M17" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>6</v>
       </c>
@@ -1248,23 +991,8 @@
       <c r="G18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="3">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K18" s="3">
-        <v>7</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2</v>
-      </c>
-      <c r="M18" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>7</v>
       </c>
@@ -1286,60 +1014,13 @@
       <c r="G19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="3">
-        <v>19</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K19" s="3">
-        <v>3</v>
-      </c>
-      <c r="L19" s="3">
-        <v>7</v>
-      </c>
-      <c r="M19" s="3">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I20" s="3">
-        <v>20</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="3">
-        <v>7</v>
-      </c>
-      <c r="L20" s="3">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>45</v>
       </c>
-      <c r="I21" s="3">
-        <v>21</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="3">
-        <v>6</v>
-      </c>
-      <c r="L21" s="3">
-        <v>7</v>
-      </c>
-      <c r="M21" s="3">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
@@ -1355,23 +1036,8 @@
       <c r="E22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="3">
-        <v>22</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K22" s="3">
-        <v>7</v>
-      </c>
-      <c r="L22" s="3">
-        <v>6</v>
-      </c>
-      <c r="M22" s="3">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>1</v>
       </c>
@@ -1387,23 +1053,8 @@
       <c r="E23" s="3">
         <v>90</v>
       </c>
-      <c r="I23" s="3">
-        <v>23</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K23" s="3">
-        <v>4</v>
-      </c>
-      <c r="L23" s="3">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>2</v>
       </c>
@@ -1419,23 +1070,8 @@
       <c r="E24" s="3">
         <v>90</v>
       </c>
-      <c r="I24" s="3">
-        <v>24</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>3</v>
       </c>
@@ -1451,23 +1087,8 @@
       <c r="E25" s="3">
         <v>240</v>
       </c>
-      <c r="I25" s="3">
-        <v>25</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K25" s="3">
-        <v>4</v>
-      </c>
-      <c r="L25" s="3">
-        <v>3</v>
-      </c>
-      <c r="M25" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>4</v>
       </c>
@@ -1483,23 +1104,8 @@
       <c r="E26" s="3">
         <v>240</v>
       </c>
-      <c r="I26" s="3">
-        <v>26</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="3">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
-        <v>4</v>
-      </c>
-      <c r="M26" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>5</v>
       </c>
@@ -1515,23 +1121,8 @@
       <c r="E27" s="3">
         <v>180</v>
       </c>
-      <c r="I27" s="3">
-        <v>27</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="3">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3">
-        <v>6</v>
-      </c>
-      <c r="M27" s="3">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>6</v>
       </c>
@@ -1547,23 +1138,8 @@
       <c r="E28" s="3">
         <v>180</v>
       </c>
-      <c r="I28" s="3">
-        <v>28</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K28" s="3">
-        <v>6</v>
-      </c>
-      <c r="L28" s="3">
-        <v>4</v>
-      </c>
-      <c r="M28" s="3">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>7</v>
       </c>
@@ -1579,23 +1155,8 @@
       <c r="E29" s="3">
         <v>350</v>
       </c>
-      <c r="I29" s="3">
-        <v>29</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K29" s="3">
-        <v>2</v>
-      </c>
-      <c r="L29" s="3">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>8</v>
       </c>
@@ -1611,23 +1172,8 @@
       <c r="E30" s="3">
         <v>350</v>
       </c>
-      <c r="I30" s="3">
-        <v>30</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K30" s="3">
-        <v>3</v>
-      </c>
-      <c r="L30" s="3">
-        <v>2</v>
-      </c>
-      <c r="M30" s="3">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>9</v>
       </c>
@@ -1643,23 +1189,8 @@
       <c r="E31" s="3">
         <v>240</v>
       </c>
-      <c r="I31" s="3">
-        <v>31</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K31" s="3">
-        <v>2</v>
-      </c>
-      <c r="L31" s="3">
-        <v>6</v>
-      </c>
-      <c r="M31" s="3">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>10</v>
       </c>
@@ -1675,23 +1206,8 @@
       <c r="E32" s="3">
         <v>240</v>
       </c>
-      <c r="I32" s="3">
-        <v>32</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K32" s="3">
-        <v>6</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2</v>
-      </c>
-      <c r="M32" s="3">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>11</v>
       </c>
@@ -1707,23 +1223,8 @@
       <c r="E33" s="3">
         <v>320</v>
       </c>
-      <c r="I33" s="3">
-        <v>33</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K33" s="3">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1</v>
-      </c>
-      <c r="M33" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>12</v>
       </c>
@@ -1739,23 +1240,8 @@
       <c r="E34" s="3">
         <v>320</v>
       </c>
-      <c r="I34" s="3">
-        <v>34</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K34" s="3">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3">
-        <v>4</v>
-      </c>
-      <c r="M34" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>13</v>
       </c>
@@ -1771,23 +1257,8 @@
       <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
-        <v>35</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
-        <v>7</v>
-      </c>
-      <c r="M35" s="3">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>14</v>
       </c>
@@ -1803,23 +1274,8 @@
       <c r="E36" s="3">
         <v>500</v>
       </c>
-      <c r="I36" s="3">
-        <v>36</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K36" s="3">
-        <v>7</v>
-      </c>
-      <c r="L36" s="3">
-        <v>5</v>
-      </c>
-      <c r="M36" s="3">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>15</v>
       </c>
@@ -1835,23 +1291,8 @@
       <c r="E37" s="3">
         <v>550</v>
       </c>
-      <c r="I37" s="3">
-        <v>37</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K37" s="3">
-        <v>3</v>
-      </c>
-      <c r="L37" s="3">
-        <v>4</v>
-      </c>
-      <c r="M37" s="3">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>16</v>
       </c>
@@ -1867,23 +1308,8 @@
       <c r="E38" s="3">
         <v>550</v>
       </c>
-      <c r="I38" s="3">
-        <v>38</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K38" s="3">
-        <v>4</v>
-      </c>
-      <c r="L38" s="3">
-        <v>3</v>
-      </c>
-      <c r="M38" s="3">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>17</v>
       </c>
@@ -1899,23 +1325,8 @@
       <c r="E39" s="3">
         <v>300</v>
       </c>
-      <c r="I39" s="3">
-        <v>39</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1</v>
-      </c>
-      <c r="L39" s="3">
-        <v>7</v>
-      </c>
-      <c r="M39" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>18</v>
       </c>
@@ -1931,23 +1342,8 @@
       <c r="E40" s="3">
         <v>300</v>
       </c>
-      <c r="I40" s="3">
-        <v>40</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K40" s="3">
-        <v>7</v>
-      </c>
-      <c r="L40" s="3">
-        <v>1</v>
-      </c>
-      <c r="M40" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>19</v>
       </c>
@@ -1963,23 +1359,8 @@
       <c r="E41" s="3">
         <v>650</v>
       </c>
-      <c r="I41" s="3">
-        <v>41</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K41" s="3">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
-        <v>2</v>
-      </c>
-      <c r="M41" s="3">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>20</v>
       </c>
@@ -1995,23 +1376,8 @@
       <c r="E42" s="3">
         <v>650</v>
       </c>
-      <c r="I42" s="3">
-        <v>42</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K42" s="3">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3">
-        <v>5</v>
-      </c>
-      <c r="M42" s="3">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>21</v>
       </c>
@@ -2028,7 +1394,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>22</v>
       </c>
@@ -2045,7 +1411,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>23</v>
       </c>
@@ -2062,7 +1428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>24</v>
       </c>
@@ -2079,7 +1445,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>25</v>
       </c>
@@ -2096,7 +1462,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>26</v>
       </c>

--- a/documentacion/Catalogo de Datos.xlsx
+++ b/documentacion/Catalogo de Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322C43CD-C6DB-4AB5-95CD-31B733AD7A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C81CC6B-307C-4DDC-8935-25D6F8CAFF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F831B13-9E82-406B-B02D-1EAF59D96BE3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="390">
   <si>
     <t>numero</t>
   </si>
@@ -348,6 +348,864 @@
   </si>
   <si>
     <t>MAN Lion’s Coach</t>
+  </si>
+  <si>
+    <t>Taquilleros</t>
+  </si>
+  <si>
+    <t>registro</t>
+  </si>
+  <si>
+    <t>taqNombre</t>
+  </si>
+  <si>
+    <t>taqPrimerApell</t>
+  </si>
+  <si>
+    <t>taqSegundoApell</t>
+  </si>
+  <si>
+    <t>fechaContrato</t>
+  </si>
+  <si>
+    <t>usuario</t>
+  </si>
+  <si>
+    <t>contraseña</t>
+  </si>
+  <si>
+    <t>terminal</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Gómez</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
+  </si>
+  <si>
+    <t>agomez</t>
+  </si>
+  <si>
+    <t>AG2023</t>
+  </si>
+  <si>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>Sánchez</t>
+  </si>
+  <si>
+    <t>López</t>
+  </si>
+  <si>
+    <t>msanchez</t>
+  </si>
+  <si>
+    <t>MS22</t>
+  </si>
+  <si>
+    <t>Brenda</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Aguilar</t>
+  </si>
+  <si>
+    <t>btorres</t>
+  </si>
+  <si>
+    <t>BT24</t>
+  </si>
+  <si>
+    <t>José</t>
+  </si>
+  <si>
+    <t>Pérez</t>
+  </si>
+  <si>
+    <t>Méndez</t>
+  </si>
+  <si>
+    <t>jperez</t>
+  </si>
+  <si>
+    <t>JP24</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>Ramírez</t>
+  </si>
+  <si>
+    <t>Soto</t>
+  </si>
+  <si>
+    <t>dramirez</t>
+  </si>
+  <si>
+    <t>DR23</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Herrera</t>
+  </si>
+  <si>
+    <t>Salas</t>
+  </si>
+  <si>
+    <t>kherrera</t>
+  </si>
+  <si>
+    <t>KH25</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Díaz</t>
+  </si>
+  <si>
+    <t>lsanchez</t>
+  </si>
+  <si>
+    <t>LS22</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Medina</t>
+  </si>
+  <si>
+    <t>cmedina</t>
+  </si>
+  <si>
+    <t>CM23</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>Reyes</t>
+  </si>
+  <si>
+    <t>freyes</t>
+  </si>
+  <si>
+    <t>FR25</t>
+  </si>
+  <si>
+    <t>ctorres</t>
+  </si>
+  <si>
+    <t>CT21</t>
+  </si>
+  <si>
+    <t>Ivana</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>icruz</t>
+  </si>
+  <si>
+    <t>IC22</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Ortega</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>sortega</t>
+  </si>
+  <si>
+    <t>SO24</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>Delgado</t>
+  </si>
+  <si>
+    <t>Montoya</t>
+  </si>
+  <si>
+    <t>sdelgado</t>
+  </si>
+  <si>
+    <t>SD23</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>Tapia</t>
+  </si>
+  <si>
+    <t>vmunoz</t>
+  </si>
+  <si>
+    <t>VM24</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Paredes</t>
+  </si>
+  <si>
+    <t>León</t>
+  </si>
+  <si>
+    <t>hparedes</t>
+  </si>
+  <si>
+    <t>HP22</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>Rivas</t>
+  </si>
+  <si>
+    <t>pflores</t>
+  </si>
+  <si>
+    <t>PF24</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t>Vargas</t>
+  </si>
+  <si>
+    <t>Molina</t>
+  </si>
+  <si>
+    <t>evargas</t>
+  </si>
+  <si>
+    <t>EV23</t>
+  </si>
+  <si>
+    <t>Karla</t>
+  </si>
+  <si>
+    <t>Salgado</t>
+  </si>
+  <si>
+    <t>ksalgado</t>
+  </si>
+  <si>
+    <t>KS25</t>
+  </si>
+  <si>
+    <t>Miriam</t>
+  </si>
+  <si>
+    <t>Castillo</t>
+  </si>
+  <si>
+    <t>mcastillo</t>
+  </si>
+  <si>
+    <t>MC23</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>Navarro</t>
+  </si>
+  <si>
+    <t>Beltrán</t>
+  </si>
+  <si>
+    <t>lnavarro</t>
+  </si>
+  <si>
+    <t>LN24</t>
+  </si>
+  <si>
+    <t>Sofía</t>
+  </si>
+  <si>
+    <t>Ávila</t>
+  </si>
+  <si>
+    <t>savila</t>
+  </si>
+  <si>
+    <t>SA25</t>
+  </si>
+  <si>
+    <t>conNombre</t>
+  </si>
+  <si>
+    <t>conPrimerApell</t>
+  </si>
+  <si>
+    <t>conSegundoApell</t>
+  </si>
+  <si>
+    <t>licNumero</t>
+  </si>
+  <si>
+    <t>licVencimiento</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>Hernández</t>
+  </si>
+  <si>
+    <t>BCF-2025-91342</t>
+  </si>
+  <si>
+    <t>BCF-2024-55102</t>
+  </si>
+  <si>
+    <t>Rosa</t>
+  </si>
+  <si>
+    <t>Ponce</t>
+  </si>
+  <si>
+    <t>BCF-2026-77421</t>
+  </si>
+  <si>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t>BCF-2023-10455</t>
+  </si>
+  <si>
+    <t>Daniela</t>
+  </si>
+  <si>
+    <t>BCF-2026-66790</t>
+  </si>
+  <si>
+    <t>Héctor</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>BCF-2025-22984</t>
+  </si>
+  <si>
+    <t>BCF-2024-88311</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Silva</t>
+  </si>
+  <si>
+    <t>BCF-2025-55009</t>
+  </si>
+  <si>
+    <t>Ortiz</t>
+  </si>
+  <si>
+    <t>BCF-2027-33201</t>
+  </si>
+  <si>
+    <t>BCF-2024-11798</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>BCF-2023-42055</t>
+  </si>
+  <si>
+    <t>Alejandra</t>
+  </si>
+  <si>
+    <t>Varela</t>
+  </si>
+  <si>
+    <t>BCF-2026-90021</t>
+  </si>
+  <si>
+    <t>Conductores</t>
+  </si>
+  <si>
+    <t>paNombre</t>
+  </si>
+  <si>
+    <t>paPrimerApell</t>
+  </si>
+  <si>
+    <t>paSegundoApell</t>
+  </si>
+  <si>
+    <t>fechaNacimiento</t>
+  </si>
+  <si>
+    <t>edad</t>
+  </si>
+  <si>
+    <t>Alejandro</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>Martínez</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>Mateo</t>
+  </si>
+  <si>
+    <t>García</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>Rivera</t>
+  </si>
+  <si>
+    <t>Iván</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>Romero</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Camacho</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Rojas</t>
+  </si>
+  <si>
+    <t>Jesús</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>Cabrera</t>
+  </si>
+  <si>
+    <t>Solís</t>
+  </si>
+  <si>
+    <t>Villalobos</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Cárdenas</t>
+  </si>
+  <si>
+    <t>Elisa</t>
+  </si>
+  <si>
+    <t>Omar</t>
+  </si>
+  <si>
+    <t>Lozano</t>
+  </si>
+  <si>
+    <t>Natalia</t>
+  </si>
+  <si>
+    <t>Bernal</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Castro</t>
+  </si>
+  <si>
+    <t>Ríos</t>
+  </si>
+  <si>
+    <t>Esteban</t>
+  </si>
+  <si>
+    <t>Salinas</t>
+  </si>
+  <si>
+    <t>Duarte</t>
+  </si>
+  <si>
+    <t>Julieta</t>
+  </si>
+  <si>
+    <t>Campos</t>
+  </si>
+  <si>
+    <t>Lara</t>
+  </si>
+  <si>
+    <t>Christian</t>
+  </si>
+  <si>
+    <t>Carrillo</t>
+  </si>
+  <si>
+    <t>Peña</t>
+  </si>
+  <si>
+    <t>Marcela</t>
+  </si>
+  <si>
+    <t>Fierro</t>
+  </si>
+  <si>
+    <t>Castañeda</t>
+  </si>
+  <si>
+    <t>Rosas</t>
+  </si>
+  <si>
+    <t>Serrano</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>Maldonado</t>
+  </si>
+  <si>
+    <t>Márquez</t>
+  </si>
+  <si>
+    <t>Paulina</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Gallardo</t>
+  </si>
+  <si>
+    <t>Camila</t>
+  </si>
+  <si>
+    <t>Zoe</t>
+  </si>
+  <si>
+    <t>Emiliano</t>
+  </si>
+  <si>
+    <t>Valentina</t>
+  </si>
+  <si>
+    <t>Karina</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>Ochoa</t>
+  </si>
+  <si>
+    <t>Rentería</t>
+  </si>
+  <si>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>Robles</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Cota</t>
+  </si>
+  <si>
+    <t>Guerrero</t>
+  </si>
+  <si>
+    <t>Valdez</t>
+  </si>
+  <si>
+    <t>Ruelas</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Estrada</t>
+  </si>
+  <si>
+    <t>Quiroz</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Solano</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Murillo</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Rosales</t>
+  </si>
+  <si>
+    <t>Páez</t>
+  </si>
+  <si>
+    <t>Liliana</t>
+  </si>
+  <si>
+    <t>Lugo</t>
+  </si>
+  <si>
+    <t>Andrés</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Camargo</t>
+  </si>
+  <si>
+    <t>Félix</t>
+  </si>
+  <si>
+    <t>Rebeca</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>Cortés</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>Vázquez</t>
+  </si>
+  <si>
+    <t>Jazmín</t>
+  </si>
+  <si>
+    <t>Saúl</t>
+  </si>
+  <si>
+    <t>Zepeda</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>Zúñiga</t>
+  </si>
+  <si>
+    <t>Ximena</t>
+  </si>
+  <si>
+    <t>Rodrigo</t>
+  </si>
+  <si>
+    <t>Olivares</t>
+  </si>
+  <si>
+    <t>Sepúlveda</t>
+  </si>
+  <si>
+    <t>Valenzuela</t>
+  </si>
+  <si>
+    <t>Manuel</t>
+  </si>
+  <si>
+    <t>Irma</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>González</t>
+  </si>
+  <si>
+    <t>Petra</t>
+  </si>
+  <si>
+    <t>Tomás</t>
+  </si>
+  <si>
+    <t>Luz</t>
+  </si>
+  <si>
+    <t>Chávez</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>Josefina</t>
+  </si>
+  <si>
+    <t>Acosta</t>
+  </si>
+  <si>
+    <t>Padilla</t>
+  </si>
+  <si>
+    <t>Yesenia</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>Rocha</t>
+  </si>
+  <si>
+    <t>Figueroa</t>
+  </si>
+  <si>
+    <t>Celeste</t>
+  </si>
+  <si>
+    <t>Villar</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>Verónica</t>
+  </si>
+  <si>
+    <t>Aldo</t>
+  </si>
+  <si>
+    <t>Aguirre</t>
+  </si>
+  <si>
+    <t>Rodríguez</t>
+  </si>
+  <si>
+    <t>Lozoya</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>Joaquín</t>
+  </si>
+  <si>
+    <t>Pineda</t>
+  </si>
+  <si>
+    <t>Pamela</t>
+  </si>
+  <si>
+    <t>Damián</t>
+  </si>
+  <si>
+    <t>Estefanía</t>
+  </si>
+  <si>
+    <t>Montaño</t>
+  </si>
+  <si>
+    <t>Pacheco</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>Mejía</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <t>Ibarra</t>
+  </si>
+  <si>
+    <t>Pasajeros</t>
+  </si>
+  <si>
+    <t>PLU</t>
+  </si>
+  <si>
+    <t>Plus</t>
+  </si>
+  <si>
+    <t>DIS</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>Comun</t>
+  </si>
+  <si>
+    <t>Tipo_Asiento</t>
   </si>
 </sst>
 </file>
@@ -406,7 +1264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -419,6 +1277,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,8 +1615,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D33CE82-57EC-47E4-9B49-5C264FA2EEA8}">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:I252"/>
   <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2071,6 +2938,3086 @@
         <v>4</v>
       </c>
     </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="3">
+        <v>1</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E100" s="5">
+        <v>44936</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="3">
+        <v>2</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E101" s="5">
+        <v>45007</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="3">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E102" s="5">
+        <v>45488</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H102" s="3">
+        <v>1</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="3">
+        <v>4</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E103" s="5">
+        <v>45387</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H103" s="3">
+        <v>2</v>
+      </c>
+      <c r="I103" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="3">
+        <v>5</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E104" s="5">
+        <v>45210</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H104" s="3">
+        <v>2</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="3">
+        <v>6</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E105" s="5">
+        <v>45675</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H105" s="3">
+        <v>2</v>
+      </c>
+      <c r="I105" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="3">
+        <v>7</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E106" s="5">
+        <v>44818</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H106" s="3">
+        <v>3</v>
+      </c>
+      <c r="I106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="3">
+        <v>8</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E107" s="5">
+        <v>45049</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H107" s="3">
+        <v>3</v>
+      </c>
+      <c r="I107" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="3">
+        <v>9</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" s="5">
+        <v>45658</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H108" s="3">
+        <v>3</v>
+      </c>
+      <c r="I108" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="3">
+        <v>10</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E109" s="5">
+        <v>44246</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H109" s="3">
+        <v>4</v>
+      </c>
+      <c r="I109" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="3">
+        <v>11</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E110" s="5">
+        <v>44802</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H110" s="3">
+        <v>4</v>
+      </c>
+      <c r="I110" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="3">
+        <v>12</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E111" s="5">
+        <v>45336</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H111" s="3">
+        <v>4</v>
+      </c>
+      <c r="I111" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="3">
+        <v>13</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E112" s="5">
+        <v>45089</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H112" s="3">
+        <v>5</v>
+      </c>
+      <c r="I112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="3">
+        <v>14</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E113" s="5">
+        <v>45295</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H113" s="3">
+        <v>5</v>
+      </c>
+      <c r="I113" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="3">
+        <v>15</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E114" s="5">
+        <v>44885</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H114" s="3">
+        <v>5</v>
+      </c>
+      <c r="I114" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="3">
+        <v>16</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E115" s="5">
+        <v>45431</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H115" s="3">
+        <v>6</v>
+      </c>
+      <c r="I115" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="3">
+        <v>17</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="5">
+        <v>44987</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H116" s="3">
+        <v>6</v>
+      </c>
+      <c r="I116" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="3">
+        <v>18</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E117" s="5">
+        <v>45695</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H117" s="3">
+        <v>6</v>
+      </c>
+      <c r="I117" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="3">
+        <v>19</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E118" s="5">
+        <v>45199</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H118" s="3">
+        <v>7</v>
+      </c>
+      <c r="I118" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="3">
+        <v>20</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" s="5">
+        <v>45372</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H119" s="3">
+        <v>7</v>
+      </c>
+      <c r="I119" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="3">
+        <v>21</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E120" s="5">
+        <v>45670</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H120" s="3">
+        <v>7</v>
+      </c>
+      <c r="I120" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="3">
+        <v>1</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F124" s="5">
+        <v>46855</v>
+      </c>
+      <c r="G124" s="5">
+        <v>44630</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="3">
+        <v>2</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F125" s="5">
+        <v>46692</v>
+      </c>
+      <c r="G125" s="5">
+        <v>44391</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="3">
+        <v>3</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F126" s="5">
+        <v>47169</v>
+      </c>
+      <c r="G126" s="5">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="3">
+        <v>4</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F127" s="5">
+        <v>46660</v>
+      </c>
+      <c r="G127" s="5">
+        <v>43973</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="3">
+        <v>5</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F128" s="5">
+        <v>47500</v>
+      </c>
+      <c r="G128" s="5">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="3">
+        <v>6</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F129" s="5">
+        <v>46917</v>
+      </c>
+      <c r="G129" s="5">
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="3">
+        <v>7</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F130" s="5">
+        <v>46455</v>
+      </c>
+      <c r="G130" s="5">
+        <v>44813</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="3">
+        <v>8</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F131" s="5">
+        <v>47101</v>
+      </c>
+      <c r="G131" s="5">
+        <v>44544</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="3">
+        <v>9</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F132" s="5">
+        <v>47233</v>
+      </c>
+      <c r="G132" s="5">
+        <v>44977</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="3">
+        <v>10</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F133" s="5">
+        <v>46306</v>
+      </c>
+      <c r="G133" s="5">
+        <v>45454</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="3">
+        <v>11</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F134" s="5">
+        <v>46608</v>
+      </c>
+      <c r="G134" s="5">
+        <v>45141</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="3">
+        <v>12</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F135" s="5">
+        <v>47178</v>
+      </c>
+      <c r="G135" s="5">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="3">
+        <v>1</v>
+      </c>
+      <c r="B139" s="3">
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="3">
+        <v>2</v>
+      </c>
+      <c r="B140" s="3">
+        <v>50</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="3">
+        <v>3</v>
+      </c>
+      <c r="B141" s="3">
+        <v>30</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="3">
+        <v>4</v>
+      </c>
+      <c r="B142" s="3">
+        <v>25</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="3">
+        <v>5</v>
+      </c>
+      <c r="B143" s="3">
+        <v>15</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="3">
+        <v>1</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E147" s="5">
+        <v>34801</v>
+      </c>
+      <c r="F147" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="3">
+        <v>2</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E148" s="5">
+        <v>32450</v>
+      </c>
+      <c r="F148" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="3">
+        <v>3</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E149" s="5">
+        <v>37063</v>
+      </c>
+      <c r="F149" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="3">
+        <v>4</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E150" s="5">
+        <v>36418</v>
+      </c>
+      <c r="F150" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="3">
+        <v>5</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E151" s="5">
+        <v>31816</v>
+      </c>
+      <c r="F151" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="3">
+        <v>6</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E152" s="5">
+        <v>38687</v>
+      </c>
+      <c r="F152" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="3">
+        <v>7</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E153" s="5">
+        <v>33380</v>
+      </c>
+      <c r="F153" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="3">
+        <v>8</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E154" s="5">
+        <v>34251</v>
+      </c>
+      <c r="F154" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="3">
+        <v>9</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E155" s="5">
+        <v>29294</v>
+      </c>
+      <c r="F155" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="3">
+        <v>10</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E156" s="5">
+        <v>35662</v>
+      </c>
+      <c r="F156" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="3">
+        <v>11</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E157" s="5">
+        <v>37996</v>
+      </c>
+      <c r="F157" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="3">
+        <v>12</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E158" s="5">
+        <v>31228</v>
+      </c>
+      <c r="F158" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="3">
+        <v>13</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E159" s="5">
+        <v>33942</v>
+      </c>
+      <c r="F159" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="3">
+        <v>14</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E160" s="5">
+        <v>34384</v>
+      </c>
+      <c r="F160" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="3">
+        <v>15</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E161" s="5">
+        <v>35983</v>
+      </c>
+      <c r="F161" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="3">
+        <v>16</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E162" s="5">
+        <v>32531</v>
+      </c>
+      <c r="F162" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="3">
+        <v>17</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E163" s="5">
+        <v>36644</v>
+      </c>
+      <c r="F163" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="3">
+        <v>18</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E164" s="5">
+        <v>29099</v>
+      </c>
+      <c r="F164" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="3">
+        <v>19</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E165" s="5">
+        <v>35381</v>
+      </c>
+      <c r="F165" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="3">
+        <v>20</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E166" s="5">
+        <v>30820</v>
+      </c>
+      <c r="F166" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="3">
+        <v>21</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E167" s="5">
+        <v>36241</v>
+      </c>
+      <c r="F167" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="3">
+        <v>22</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E168" s="5">
+        <v>34180</v>
+      </c>
+      <c r="F168" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="3">
+        <v>23</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E169" s="5">
+        <v>37546</v>
+      </c>
+      <c r="F169" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="3">
+        <v>24</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E170" s="5">
+        <v>32258</v>
+      </c>
+      <c r="F170" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="3">
+        <v>25</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E171" s="5">
+        <v>35493</v>
+      </c>
+      <c r="F171" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="3">
+        <v>26</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E172" s="5">
+        <v>33101</v>
+      </c>
+      <c r="F172" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="3">
+        <v>27</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E173" s="5">
+        <v>31454</v>
+      </c>
+      <c r="F173" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="3">
+        <v>28</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E174" s="5">
+        <v>37893</v>
+      </c>
+      <c r="F174" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="3">
+        <v>29</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E175" s="5">
+        <v>34860</v>
+      </c>
+      <c r="F175" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3">
+        <v>30</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E176" s="5">
+        <v>33617</v>
+      </c>
+      <c r="F176" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3">
+        <v>31</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E177" s="5">
+        <v>29770</v>
+      </c>
+      <c r="F177" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="3">
+        <v>32</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E178" s="5">
+        <v>34481</v>
+      </c>
+      <c r="F178" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3">
+        <v>33</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E179" s="5">
+        <v>36516</v>
+      </c>
+      <c r="F179" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3">
+        <v>34</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E180" s="5">
+        <v>30377</v>
+      </c>
+      <c r="F180" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3">
+        <v>35</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E181" s="5">
+        <v>28751</v>
+      </c>
+      <c r="F181" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3">
+        <v>36</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E182" s="5">
+        <v>37200</v>
+      </c>
+      <c r="F182" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="3">
+        <v>37</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E183" s="5">
+        <v>35093</v>
+      </c>
+      <c r="F183" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="3">
+        <v>38</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E184" s="5">
+        <v>38512</v>
+      </c>
+      <c r="F184" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="3">
+        <v>39</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E185" s="5">
+        <v>34080</v>
+      </c>
+      <c r="F185" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="3">
+        <v>40</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E186" s="5">
+        <v>36098</v>
+      </c>
+      <c r="F186" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="3">
+        <v>41</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E187" s="5">
+        <v>42565</v>
+      </c>
+      <c r="F187" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="3">
+        <v>42</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E188" s="5">
+        <v>42036</v>
+      </c>
+      <c r="F188" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="3">
+        <v>43</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E189" s="5">
+        <v>43062</v>
+      </c>
+      <c r="F189" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="3">
+        <v>44</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E190" s="5">
+        <v>43532</v>
+      </c>
+      <c r="F190" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="3">
+        <v>45</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E191" s="5">
+        <v>41907</v>
+      </c>
+      <c r="F191" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="3">
+        <v>46</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E192" s="5">
+        <v>43464</v>
+      </c>
+      <c r="F192" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="3">
+        <v>47</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E193" s="5">
+        <v>32966</v>
+      </c>
+      <c r="F193" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="3">
+        <v>48</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E194" s="5">
+        <v>32126</v>
+      </c>
+      <c r="F194" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="3">
+        <v>49</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E195" s="5">
+        <v>34664</v>
+      </c>
+      <c r="F195" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="3">
+        <v>50</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E196" s="5">
+        <v>31261</v>
+      </c>
+      <c r="F196" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="3">
+        <v>51</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E197" s="5">
+        <v>36307</v>
+      </c>
+      <c r="F197" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="3">
+        <v>52</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E198" s="5">
+        <v>37275</v>
+      </c>
+      <c r="F198" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="3">
+        <v>53</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E199" s="5">
+        <v>33400</v>
+      </c>
+      <c r="F199" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="3">
+        <v>54</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E200" s="5">
+        <v>37901</v>
+      </c>
+      <c r="F200" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="3">
+        <v>55</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E201" s="5">
+        <v>35322</v>
+      </c>
+      <c r="F201" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="3">
+        <v>56</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E202" s="5">
+        <v>29342</v>
+      </c>
+      <c r="F202" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="3">
+        <v>57</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E203" s="5">
+        <v>32205</v>
+      </c>
+      <c r="F203" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="3">
+        <v>58</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E204" s="5">
+        <v>34018</v>
+      </c>
+      <c r="F204" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="3">
+        <v>59</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E205" s="5">
+        <v>31755</v>
+      </c>
+      <c r="F205" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="3">
+        <v>60</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E206" s="5">
+        <v>35550</v>
+      </c>
+      <c r="F206" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="3">
+        <v>61</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E207" s="5">
+        <v>30879</v>
+      </c>
+      <c r="F207" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="3">
+        <v>62</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E208" s="5">
+        <v>33144</v>
+      </c>
+      <c r="F208" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="3">
+        <v>63</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E209" s="5">
+        <v>35817</v>
+      </c>
+      <c r="F209" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" s="3">
+        <v>64</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E210" s="5">
+        <v>34977</v>
+      </c>
+      <c r="F210" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" s="3">
+        <v>65</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E211" s="5">
+        <v>33705</v>
+      </c>
+      <c r="F211" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" s="3">
+        <v>66</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E212" s="5">
+        <v>30496</v>
+      </c>
+      <c r="F212" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" s="3">
+        <v>67</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E213" s="5">
+        <v>28862</v>
+      </c>
+      <c r="F213" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="3">
+        <v>68</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E214" s="5">
+        <v>32564</v>
+      </c>
+      <c r="F214" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="3">
+        <v>69</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E215" s="5">
+        <v>37091</v>
+      </c>
+      <c r="F215" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="3">
+        <v>70</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E216" s="5">
+        <v>34609</v>
+      </c>
+      <c r="F216" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" s="3">
+        <v>71</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E217" s="5">
+        <v>20191</v>
+      </c>
+      <c r="F217" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" s="3">
+        <v>72</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E218" s="5">
+        <v>17859</v>
+      </c>
+      <c r="F218" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" s="3">
+        <v>73</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E219" s="5">
+        <v>19146</v>
+      </c>
+      <c r="F219" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="3">
+        <v>74</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E220" s="5">
+        <v>16482</v>
+      </c>
+      <c r="F220" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" s="3">
+        <v>75</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E221" s="5">
+        <v>21458</v>
+      </c>
+      <c r="F221" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="3">
+        <v>76</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E222" s="5">
+        <v>18350</v>
+      </c>
+      <c r="F222" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="3">
+        <v>77</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E223" s="5">
+        <v>14595</v>
+      </c>
+      <c r="F223" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="3">
+        <v>78</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E224" s="5">
+        <v>20654</v>
+      </c>
+      <c r="F224" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="3">
+        <v>79</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E225" s="5">
+        <v>17449</v>
+      </c>
+      <c r="F225" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="3">
+        <v>80</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E226" s="5">
+        <v>19749</v>
+      </c>
+      <c r="F226" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="3">
+        <v>81</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="E227" s="5">
+        <v>32763</v>
+      </c>
+      <c r="F227" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228" s="3">
+        <v>82</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E228" s="5">
+        <v>34029</v>
+      </c>
+      <c r="F228" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229" s="3">
+        <v>83</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E229" s="5">
+        <v>31918</v>
+      </c>
+      <c r="F229" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230" s="3">
+        <v>84</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E230" s="5">
+        <v>36208</v>
+      </c>
+      <c r="F230" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231" s="3">
+        <v>85</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E231" s="5">
+        <v>33546</v>
+      </c>
+      <c r="F231" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="3">
+        <v>86</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E232" s="5">
+        <v>35245</v>
+      </c>
+      <c r="F232" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="3">
+        <v>87</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E233" s="5">
+        <v>31243</v>
+      </c>
+      <c r="F233" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="3">
+        <v>88</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E234" s="5">
+        <v>36812</v>
+      </c>
+      <c r="F234" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235" s="3">
+        <v>89</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E235" s="5">
+        <v>29953</v>
+      </c>
+      <c r="F235" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236" s="3">
+        <v>90</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E236" s="5">
+        <v>34967</v>
+      </c>
+      <c r="F236" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237" s="3">
+        <v>91</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E237" s="5">
+        <v>35498</v>
+      </c>
+      <c r="F237" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238" s="3">
+        <v>92</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E238" s="5">
+        <v>34547</v>
+      </c>
+      <c r="F238" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239" s="3">
+        <v>93</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E239" s="5">
+        <v>37969</v>
+      </c>
+      <c r="F239" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240" s="3">
+        <v>94</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E240" s="5">
+        <v>31512</v>
+      </c>
+      <c r="F240" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241" s="3">
+        <v>95</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E241" s="5">
+        <v>32199</v>
+      </c>
+      <c r="F241" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242" s="3">
+        <v>96</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E242" s="5">
+        <v>33183</v>
+      </c>
+      <c r="F242" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243" s="3">
+        <v>97</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E243" s="5">
+        <v>33754</v>
+      </c>
+      <c r="F243" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" s="3">
+        <v>98</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E244" s="5">
+        <v>36906</v>
+      </c>
+      <c r="F244" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245" s="3">
+        <v>99</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E245" s="5">
+        <v>35979</v>
+      </c>
+      <c r="F245" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246" s="3">
+        <v>100</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E246" s="5">
+        <v>30609</v>
+      </c>
+      <c r="F246" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documentacion/Catalogo de Datos.xlsx
+++ b/documentacion/Catalogo de Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C81CC6B-307C-4DDC-8935-25D6F8CAFF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E1012C-A48A-492A-BE6F-E33C3B89F31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F831B13-9E82-406B-B02D-1EAF59D96BE3}"/>
   </bookViews>

--- a/documentacion/Catalogo de Datos.xlsx
+++ b/documentacion/Catalogo de Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165C5024-5BC0-4847-897B-3DAD19F09CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5667437E-59CC-44B7-B5A3-D29E7D8E38DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F831B13-9E82-406B-B02D-1EAF59D96BE3}"/>
   </bookViews>
@@ -2017,7 +2017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>7</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>1</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>4</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>5</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>4</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>5</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>2</v>
       </c>
       <c r="B768" s="6">
-        <v>45668.375</v>
+        <v>45667.375</v>
       </c>
       <c r="C768" s="6">
         <v>45668.5625</v>

--- a/documentacion/Catalogo de Datos.xlsx
+++ b/documentacion/Catalogo de Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shavi\Downloads\visual\Proyecto\RBE\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E9EB16-2E2E-4883-BA7F-C0992567204F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E6CED6-5462-4562-80BB-8EA9223BE060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{ED69D29D-1770-49DF-9C6B-DA0D835AFA89}"/>
   </bookViews>
@@ -17961,12 +17961,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup scale="63" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="59" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;RPagina &amp;P</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="74" max="16383" man="1"/>
+  <rowBreaks count="6" manualBreakCount="6">
+    <brk id="71" max="16383" man="1"/>
+    <brk id="142" max="16383" man="1"/>
+    <brk id="213" max="16383" man="1"/>
+    <brk id="284" max="16383" man="1"/>
+    <brk id="355" max="16383" man="1"/>
+    <brk id="426" max="16383" man="1"/>
   </rowBreaks>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
